--- a/outputs/daily/predictions_2026-06-17.xlsx
+++ b/outputs/daily/predictions_2026-06-17.xlsx
@@ -1114,31 +1114,31 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>2.023059481056323</v>
+        <v>2.03810307592649</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7338336961520371</v>
+        <v>0.724290101281869</v>
       </c>
       <c r="M3" t="b">
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.739271835784143</v>
+        <v>0.7528050123775849</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1738607272502737</v>
+        <v>0.1686942506292952</v>
       </c>
       <c r="P3" t="n">
-        <v>0.08686743696558327</v>
+        <v>0.07850073699311992</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5369413688031004</v>
+        <v>0.5390515869680091</v>
       </c>
       <c r="R3" t="n">
-        <v>2.141329041126642</v>
+        <v>2.168681031799675</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6886709588733576</v>
+        <v>0.6713189682003248</v>
       </c>
       <c r="T3" t="n">
         <v>0.7220060645558366</v>
@@ -1156,58 +1156,58 @@
         <v>0.376246590822906</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.6661733695051605</v>
+        <v>0.6716457493335024</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.217917734936065</v>
+        <v>0.2155822894808193</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.1159088955587749</v>
+        <v>0.1127719611856784</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.5202035661421989</v>
+        <v>0.5215292592959694</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.4797964338578011</v>
+        <v>0.4784707407040306</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4605983653369395</v>
+        <v>0.4575164559173733</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.5394016346630606</v>
+        <v>0.5424835440826267</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.668015</v>
+        <v>0.672785</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.21672</v>
+        <v>0.214445</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.115265</v>
+        <v>0.11277</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.520045</v>
+        <v>0.52167</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.45978</v>
+        <v>0.45718</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.024365</v>
+        <v>2.03894</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.73192</v>
+        <v>0.724325</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.756285</v>
+        <v>2.763265</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.7149541992844901</v>
+        <v>0.7217355648789523</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.1831146294157503</v>
+        <v>0.1804641774035475</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.1019311712997597</v>
+        <v>0.0978002577175002</v>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="AR3" t="n">
-        <v>0.7149541992844901</v>
+        <v>0.7217355648789523</v>
       </c>
       <c r="AS3" t="b">
         <v>1</v>
@@ -1227,20 +1227,20 @@
       <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>UNDER_2_5</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2.159553742503904</v>
+        <v>12.73873390625165</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.4797964338578011</v>
+        <v>0.0978002577175002</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.01673780266090141</v>
+        <v>0.01929952072438028</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.03614618437764139</v>
+        <v>0.2458514590260696</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="BE3" t="n">
-        <v>0.1299235333683849</v>
+        <v>0.1311397858468235</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="BG3" t="n">
-        <v>0.1190170707532922</v>
+        <v>0.1193673297551149</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="BI3" t="n">
-        <v>0.1036810774589579</v>
+        <v>0.1025282527507992</v>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>0.09534226670885443</v>
+        <v>0.0949832487730784</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>0.08761434533108288</v>
+        <v>0.08909213363691741</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="BO3" t="n">
-        <v>0.072914849005977</v>
+        <v>0.07246185509664078</v>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="BQ3" t="n">
-        <v>0.06429435887024952</v>
+        <v>0.06452855049530072</v>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="BS3" t="n">
-        <v>0.04431225799964748</v>
+        <v>0.04539473790156382</v>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="BU3" t="n">
-        <v>0.03716503262754283</v>
+        <v>0.03641172697429729</v>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="BW3" t="n">
-        <v>0.03498268398923598</v>
+        <v>0.03439771343696697</v>
       </c>
     </row>
     <row r="4">
@@ -1373,31 +1373,31 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1.650296373620825</v>
+        <v>1.684231463320184</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8912375735246004</v>
+        <v>0.8958024838252415</v>
       </c>
       <c r="M4" t="b">
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5530901971634742</v>
+        <v>0.560712723672835</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2572900933284754</v>
+        <v>0.2565419979077691</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1896197095080504</v>
+        <v>0.1827452784193959</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4423901650422317</v>
+        <v>0.4622765123361929</v>
       </c>
       <c r="R4" t="n">
-        <v>1.61467216297497</v>
+        <v>1.676372326064713</v>
       </c>
       <c r="S4" t="n">
-        <v>0.83532783702503</v>
+        <v>0.8436276739352865</v>
       </c>
       <c r="T4" t="n">
         <v>0.5749977118420153</v>
@@ -1415,58 +1415,58 @@
         <v>0.4957734266643557</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5412344422809714</v>
+        <v>0.5484805461709247</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2679547985641457</v>
+        <v>0.2640274894627461</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1908107591548831</v>
+        <v>0.1874919643663293</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.466795160284482</v>
+        <v>0.4765457107982738</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.533204839715518</v>
+        <v>0.5234542892017262</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4881864645197723</v>
+        <v>0.4933363590139911</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.5118135354802278</v>
+        <v>0.5066636409860088</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.54225</v>
+        <v>0.54941</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.266515</v>
+        <v>0.26282</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.191235</v>
+        <v>0.18777</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.46669</v>
+        <v>0.47637</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.48739</v>
+        <v>0.492255</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.651075</v>
+        <v>1.685055</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.89071</v>
+        <v>0.89507</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.541785</v>
+        <v>2.580125</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.557793888580338</v>
+        <v>0.5626544251565706</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.2563239714882668</v>
+        <v>0.2550429060446344</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.1858821399313954</v>
+        <v>0.1823026687987951</v>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
@@ -1474,44 +1474,32 @@
         </is>
       </c>
       <c r="AR4" t="n">
-        <v>0.557793888580338</v>
+        <v>0.5626544251565706</v>
       </c>
       <c r="AS4" t="b">
         <v>1</v>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>OVER_2_5</t>
         </is>
       </c>
-      <c r="AU4" t="n">
-        <v>2.260448081852221</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.466795160284482</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.02440499524225032</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0.05516622468295718</v>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>OVER_2_5</t>
-        </is>
-      </c>
       <c r="AZ4" t="n">
-        <v>2.260448081852221</v>
+        <v>2.163207459851962</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.466795160284482</v>
+        <v>0.4765457107982738</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.02440499524225032</v>
+        <v>0.01426919846208091</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.05516622468295718</v>
+        <v>0.0308672365592817</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -1519,7 +1507,7 @@
         </is>
       </c>
       <c r="BE4" t="n">
-        <v>0.1274015020701184</v>
+        <v>0.1257514333202072</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -1527,7 +1515,7 @@
         </is>
       </c>
       <c r="BG4" t="n">
-        <v>0.1183716634452148</v>
+        <v>0.1161848944038379</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
@@ -1535,7 +1523,7 @@
         </is>
       </c>
       <c r="BI4" t="n">
-        <v>0.1072309924097406</v>
+        <v>0.1074681510203523</v>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
@@ -1543,7 +1531,7 @@
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>0.09556828948189203</v>
+        <v>0.09627023661613775</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
@@ -1551,7 +1539,7 @@
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>0.09032757900823589</v>
+        <v>0.08720350700561609</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
@@ -1559,7 +1547,7 @@
         </is>
       </c>
       <c r="BO4" t="n">
-        <v>0.05898763930451904</v>
+        <v>0.06033374708444083</v>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
@@ -1567,7 +1555,7 @@
         </is>
       </c>
       <c r="BQ4" t="n">
-        <v>0.05859910437051723</v>
+        <v>0.05644440184362701</v>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
@@ -1575,7 +1563,7 @@
         </is>
       </c>
       <c r="BS4" t="n">
-        <v>0.0525720005217039</v>
+        <v>0.05404712049672603</v>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
@@ -1583,7 +1571,7 @@
         </is>
       </c>
       <c r="BU4" t="n">
-        <v>0.05161136616743713</v>
+        <v>0.05120383923310265</v>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
@@ -1591,7 +1579,7 @@
         </is>
       </c>
       <c r="BW4" t="n">
-        <v>0.04258702521186902</v>
+        <v>0.04311955853958995</v>
       </c>
     </row>
     <row r="5">
@@ -1644,31 +1632,31 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>1.261073421261813</v>
+        <v>1.225646232699302</v>
       </c>
       <c r="L5" t="n">
-        <v>1.277464196318647</v>
+        <v>1.285391384881157</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4280058986884045</v>
+        <v>0.4075238068285265</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2930255661763326</v>
+        <v>0.2991097735458874</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2789685351352629</v>
+        <v>0.293366419625586</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4187477988178553</v>
+        <v>0.4058155707644355</v>
       </c>
       <c r="R5" t="n">
-        <v>1.341691360219359</v>
+        <v>1.277278290105703</v>
       </c>
       <c r="S5" t="n">
-        <v>1.018308639780641</v>
+        <v>1.032721709894297</v>
       </c>
       <c r="T5" t="n">
         <v>0.3274886686669227</v>
@@ -1686,58 +1674,58 @@
         <v>0.4859334769718118</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3495847528985815</v>
+        <v>0.3384001586037123</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.2930699491000796</v>
+        <v>0.2947820772678271</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.3573452980013389</v>
+        <v>0.3668177641284606</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.4660334979237972</v>
+        <v>0.4590149564400331</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.5339665020762028</v>
+        <v>0.5409850435599669</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.5296126054867248</v>
+        <v>0.523863671838695</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.4703873945132752</v>
+        <v>0.476136328161305</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.34819</v>
+        <v>0.337535</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.29243</v>
+        <v>0.29342</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.35938</v>
+        <v>0.369045</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.46684</v>
+        <v>0.459405</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.530245</v>
+        <v>0.52406</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.25988</v>
+        <v>1.22484</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.283405</v>
+        <v>1.287645</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.543285</v>
+        <v>2.512485</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.3732195817334301</v>
+        <v>0.3622305964157617</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.2856775733278229</v>
+        <v>0.2885392883175817</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.341102844938747</v>
+        <v>0.3492301152666566</v>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
         </is>
       </c>
       <c r="AR5" t="n">
-        <v>0.3732195817334301</v>
+        <v>0.3622305964157617</v>
       </c>
       <c r="AS5" t="b">
         <v>1</v>
@@ -1756,16 +1744,16 @@
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>3.584633655960992</v>
+        <v>3.408706426850992</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.341102844938747</v>
+        <v>0.3492301152666566</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.06213430980348406</v>
+        <v>0.05586369564107063</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.222728738111476</v>
+        <v>0.1904229383593652</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
@@ -1773,16 +1761,16 @@
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>3.584633655960992</v>
+        <v>3.408706426850992</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.341102844938747</v>
+        <v>0.3492301152666566</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.06213430980348406</v>
+        <v>0.05586369564107063</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.222728738111476</v>
+        <v>0.1904229383593652</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -1790,7 +1778,7 @@
         </is>
       </c>
       <c r="BE5" t="n">
-        <v>0.1399616357273858</v>
+        <v>0.1406900908370456</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -1798,7 +1786,7 @@
         </is>
       </c>
       <c r="BG5" t="n">
-        <v>0.09170561920964845</v>
+        <v>0.09397398206633008</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
@@ -1806,7 +1794,7 @@
         </is>
       </c>
       <c r="BI5" t="n">
-        <v>0.08817268021180159</v>
+        <v>0.09156317226584329</v>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
@@ -1814,7 +1802,7 @@
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>0.08687810673477894</v>
+        <v>0.08671282339593166</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
@@ -1822,7 +1810,7 @@
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>0.08127089931814911</v>
+        <v>0.08220083213640265</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
@@ -1830,7 +1818,7 @@
         </is>
       </c>
       <c r="BO5" t="n">
-        <v>0.08022813582369724</v>
+        <v>0.07838012718752158</v>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
@@ -1838,7 +1826,7 @@
         </is>
       </c>
       <c r="BQ5" t="n">
-        <v>0.06444581096382998</v>
+        <v>0.06706733961509241</v>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
@@ -1846,7 +1834,7 @@
         </is>
       </c>
       <c r="BS5" t="n">
-        <v>0.06280264922875803</v>
+        <v>0.06097763537972392</v>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
@@ -1854,7 +1842,7 @@
         </is>
       </c>
       <c r="BU5" t="n">
-        <v>0.05124428552608131</v>
+        <v>0.05037457011636481</v>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
@@ -1862,7 +1850,7 @@
         </is>
       </c>
       <c r="BW5" t="n">
-        <v>0.03460688802718434</v>
+        <v>0.03522008048606472</v>
       </c>
     </row>
     <row r="6">
